--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5478-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5478-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42CED50D-2DF9-4B24-85B9-1F8FD53B0AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{143107E1-C254-41B9-8A7E-B66E22C545DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E231074B-0FB2-4863-B292-A22C06009BE8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{30E60236-BB53-4C90-B650-334D49B6E258}"/>
   </bookViews>
   <sheets>
     <sheet name="5478-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1499,25 +1499,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E1AB88-CBF9-411C-9570-972F5FCA9239}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F97FE09-22FF-4E92-A488-44829BF30679}">
   <dimension ref="A1:R54"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1545,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1575,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1671,7 +1671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="40">
         <v>2024</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="38">
         <v>2023</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2022</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2021</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2020</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2019</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2018</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2017</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2016</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2015</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2014</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2013</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2012</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38">
         <v>2011</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>9.0299999999999994</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>2010</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>2009</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="40">
         <v>2008</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>8.34</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>2007</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>2006</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="38">
         <v>2005</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
         <v>2004</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>2003</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
         <v>2002</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="38">
         <v>2001</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="40">
         <v>2000</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>1999</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="40">
         <v>1998</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="38" t="s">
         <v>51</v>
       </c>
